--- a/C/01. C LANGUAGE FUNDAMENTALS.xlsx
+++ b/C/01. C LANGUAGE FUNDAMENTALS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\Kỹ Thuật lập trình\C\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORK\Home\Programming-Techniques-main\C\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" tabRatio="857"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" tabRatio="857" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="MucLuc" sheetId="11" r:id="rId1"/>
@@ -317,7 +317,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -338,7 +338,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -359,7 +359,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -394,7 +394,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -415,7 +415,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -436,7 +436,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -471,7 +471,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -492,7 +492,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -527,7 +527,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -548,7 +548,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -574,7 +574,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -595,7 +595,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -630,7 +630,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -654,7 +654,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -673,7 +673,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -692,7 +692,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -718,7 +718,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -753,7 +753,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -774,7 +774,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -809,7 +809,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -844,7 +844,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -870,7 +870,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -891,7 +891,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -940,7 +940,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -966,7 +966,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -992,7 +992,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1022,7 +1022,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1043,7 +1043,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1064,7 +1064,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1081,7 +1081,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1102,7 +1102,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1113,7 +1113,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1137,7 +1137,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1156,7 +1156,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1175,7 +1175,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1194,7 +1194,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1402,7 +1402,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1418,7 +1418,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1434,7 +1434,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1450,7 +1450,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1474,7 +1474,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1498,7 +1498,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1522,7 +1522,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1541,7 +1541,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1565,7 +1565,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1581,7 +1581,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1597,7 +1597,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1613,7 +1613,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1637,7 +1637,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1649,7 +1649,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1660,7 +1660,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1676,7 +1676,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1692,7 +1692,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1711,7 +1711,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1728,7 +1728,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1739,7 +1739,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1758,7 +1758,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1770,7 +1770,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1781,7 +1781,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1793,7 +1793,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1809,7 +1809,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1828,7 +1828,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1844,7 +1844,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1856,7 +1856,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1867,7 +1867,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1883,7 +1883,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1899,7 +1899,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1923,7 +1923,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1942,7 +1942,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1966,7 +1966,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1982,7 +1982,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1994,7 +1994,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2005,7 +2005,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2029,7 +2029,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2053,7 +2053,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2072,7 +2072,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2091,7 +2091,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2110,7 +2110,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2134,7 +2134,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2158,7 +2158,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2177,7 +2177,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2196,7 +2196,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2220,7 +2220,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2239,7 +2239,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2258,7 +2258,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2274,7 +2274,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2290,7 +2290,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2314,7 +2314,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2340,7 +2340,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2356,7 +2356,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2375,7 +2375,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2399,7 +2399,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2418,7 +2418,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2434,7 +2434,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2453,7 +2453,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2472,7 +2472,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2488,7 +2488,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2507,7 +2507,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2533,7 +2533,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2550,7 +2550,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2599,7 +2599,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2634,7 +2634,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2669,7 +2669,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2695,7 +2695,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2721,7 +2721,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2738,7 +2738,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2754,7 +2754,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2770,7 +2770,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2796,7 +2796,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2812,7 +2812,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2828,7 +2828,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2844,7 +2844,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2957,7 +2957,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2973,7 +2973,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2985,7 +2985,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2996,7 +2996,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3012,7 +3012,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3036,7 +3036,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3052,7 +3052,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3068,7 +3068,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3084,7 +3084,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3100,7 +3100,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3117,7 +3117,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3128,7 +3128,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3145,7 +3145,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3166,7 +3166,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3177,7 +3177,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3193,7 +3193,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3209,7 +3209,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3228,7 +3228,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3247,7 +3247,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3273,7 +3273,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3284,7 +3284,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3310,7 +3310,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3326,7 +3326,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3342,7 +3342,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3358,7 +3358,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3382,7 +3382,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3398,7 +3398,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3424,7 +3424,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3440,7 +3440,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3452,7 +3452,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3463,7 +3463,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3487,7 +3487,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3506,7 +3506,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3525,7 +3525,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3541,7 +3541,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3557,7 +3557,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3573,7 +3573,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3585,7 +3585,7 @@
         <i/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3596,7 +3596,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3612,7 +3612,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3628,7 +3628,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3654,7 +3654,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3670,7 +3670,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3689,7 +3689,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3706,7 +3706,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3717,7 +3717,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3733,7 +3733,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3749,7 +3749,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3768,7 +3768,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3784,7 +3784,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3803,7 +3803,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3819,7 +3819,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3844,7 +3844,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3860,7 +3860,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3876,7 +3876,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3902,7 +3902,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3919,7 +3919,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3930,7 +3930,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3942,7 +3942,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3953,7 +3953,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3970,7 +3970,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -3981,7 +3981,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -4000,7 +4000,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -4016,7 +4016,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -4028,7 +4028,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -4039,7 +4039,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5107,7 +5107,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5131,7 +5131,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5155,7 +5155,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5179,7 +5179,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5203,7 +5203,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5227,7 +5227,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5253,7 +5253,7 @@
         <i/>
         <sz val="11"/>
         <color theme="8" tint="0.39997558519241921"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5277,7 +5277,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5296,7 +5296,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8101,7 +8101,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8117,7 +8117,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8133,7 +8133,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8149,7 +8149,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8165,7 +8165,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8181,7 +8181,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8200,7 +8200,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8224,7 +8224,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8248,7 +8248,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8272,7 +8272,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8296,7 +8296,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8312,7 +8312,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8328,7 +8328,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8344,7 +8344,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8360,7 +8360,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8376,7 +8376,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8392,7 +8392,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8411,7 +8411,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8430,7 +8430,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8449,7 +8449,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8465,7 +8465,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8481,7 +8481,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8497,7 +8497,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8513,7 +8513,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8545,7 +8545,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8562,7 +8562,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8579,7 +8579,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8596,7 +8596,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8620,7 +8620,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8639,7 +8639,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8658,7 +8658,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8690,7 +8690,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8717,7 +8717,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8741,7 +8741,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8760,7 +8760,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8792,7 +8792,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8819,7 +8819,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8843,7 +8843,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8862,7 +8862,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8886,7 +8886,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8916,7 +8916,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8935,7 +8935,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8967,7 +8967,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -8991,7 +8991,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9010,7 +9010,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9029,7 +9029,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9048,7 +9048,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9067,7 +9067,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9086,7 +9086,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9110,7 +9110,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9134,7 +9134,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9157,7 +9157,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9174,7 +9174,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9191,7 +9191,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9218,7 +9218,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9235,7 +9235,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9265,7 +9265,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9284,7 +9284,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9308,7 +9308,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9327,7 +9327,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9354,7 +9354,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9373,7 +9373,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9392,7 +9392,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9416,7 +9416,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9435,7 +9435,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9473,7 +9473,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9490,7 +9490,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9510,7 +9510,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9537,7 +9537,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9567,7 +9567,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9584,7 +9584,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9614,7 +9614,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9633,7 +9633,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9652,7 +9652,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9676,7 +9676,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9706,7 +9706,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9733,7 +9733,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9750,7 +9750,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9774,7 +9774,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -9800,7 +9800,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9809,7 +9809,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9817,7 +9817,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9848,7 +9848,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9856,7 +9856,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9869,7 +9869,7 @@
     <font>
       <sz val="11"/>
       <color theme="4" tint="0.39997558519241921"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9878,7 +9878,7 @@
       <b/>
       <sz val="11"/>
       <color theme="4" tint="0.39997558519241921"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9887,7 +9887,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9896,7 +9896,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9911,7 +9911,7 @@
       <i/>
       <sz val="11"/>
       <color theme="8" tint="0.39997558519241921"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9952,7 +9952,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -9966,7 +9966,7 @@
       <b/>
       <sz val="13.5"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -10390,15 +10390,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -10414,6 +10405,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10894,296 +10894,296 @@
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:48" ht="15" thickBot="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="105" t="s">
         <v>1644</v>
       </c>
     </row>
     <row r="2" spans="1:48" ht="24" thickBot="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="101" t="s">
         <v>1573</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="105"/>
-      <c r="U2" s="105"/>
-      <c r="V2" s="105"/>
-      <c r="W2" s="106"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="102"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="102"/>
+      <c r="R2" s="102"/>
+      <c r="S2" s="102"/>
+      <c r="T2" s="102"/>
+      <c r="U2" s="102"/>
+      <c r="V2" s="102"/>
+      <c r="W2" s="103"/>
     </row>
     <row r="4" spans="1:48" ht="17.25">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="104" t="s">
         <v>1574</v>
       </c>
-      <c r="R4" s="107" t="s">
+      <c r="R4" s="104" t="s">
         <v>1575</v>
       </c>
-      <c r="AG4" s="107" t="s">
+      <c r="AG4" s="104" t="s">
         <v>1576</v>
       </c>
-      <c r="AV4" s="107" t="s">
+      <c r="AV4" s="104" t="s">
         <v>1577</v>
       </c>
     </row>
     <row r="5" spans="1:48" ht="15">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="99" t="s">
         <v>1578</v>
       </c>
-      <c r="R5" s="102" t="s">
+      <c r="R5" s="99" t="s">
         <v>1579</v>
       </c>
-      <c r="AG5" s="102" t="s">
+      <c r="AG5" s="99" t="s">
         <v>1580</v>
       </c>
-      <c r="AV5" s="102" t="s">
+      <c r="AV5" s="99" t="s">
         <v>1581</v>
       </c>
     </row>
     <row r="6" spans="1:48">
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="100" t="s">
         <v>1582</v>
       </c>
-      <c r="R6" s="103" t="s">
+      <c r="R6" s="100" t="s">
         <v>1583</v>
       </c>
-      <c r="AG6" s="103" t="s">
+      <c r="AG6" s="100" t="s">
         <v>1584</v>
       </c>
-      <c r="AV6" s="103" t="s">
+      <c r="AV6" s="100" t="s">
         <v>1585</v>
       </c>
     </row>
     <row r="7" spans="1:48">
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="100" t="s">
         <v>1586</v>
       </c>
-      <c r="R7" s="103" t="s">
+      <c r="R7" s="100" t="s">
         <v>1587</v>
       </c>
-      <c r="AG7" s="103" t="s">
+      <c r="AG7" s="100" t="s">
         <v>1588</v>
       </c>
-      <c r="AV7" s="103" t="s">
+      <c r="AV7" s="100" t="s">
         <v>1589</v>
       </c>
     </row>
     <row r="8" spans="1:48">
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="100" t="s">
         <v>1590</v>
       </c>
-      <c r="R8" s="103" t="s">
+      <c r="R8" s="100" t="s">
         <v>1591</v>
       </c>
-      <c r="AG8" s="103" t="s">
+      <c r="AG8" s="100" t="s">
         <v>1592</v>
       </c>
-      <c r="AV8" s="103" t="s">
+      <c r="AV8" s="100" t="s">
         <v>1593</v>
       </c>
     </row>
     <row r="9" spans="1:48">
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="100" t="s">
         <v>1594</v>
       </c>
-      <c r="R9" s="103" t="s">
+      <c r="R9" s="100" t="s">
         <v>1595</v>
       </c>
-      <c r="AG9" s="103" t="s">
+      <c r="AG9" s="100" t="s">
         <v>1596</v>
       </c>
-      <c r="AV9" s="103" t="s">
+      <c r="AV9" s="100" t="s">
         <v>1597</v>
       </c>
     </row>
     <row r="10" spans="1:48">
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="100" t="s">
         <v>1598</v>
       </c>
-      <c r="R10" s="103" t="s">
+      <c r="R10" s="100" t="s">
         <v>1599</v>
       </c>
-      <c r="AG10" s="102"/>
-      <c r="AV10" s="102"/>
+      <c r="AG10" s="99"/>
+      <c r="AV10" s="99"/>
     </row>
     <row r="11" spans="1:48" ht="15">
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="100" t="s">
         <v>1600</v>
       </c>
-      <c r="R11" s="102"/>
-      <c r="AG11" s="102" t="s">
+      <c r="R11" s="99"/>
+      <c r="AG11" s="99" t="s">
         <v>1601</v>
       </c>
-      <c r="AV11" s="102" t="s">
+      <c r="AV11" s="99" t="s">
         <v>1602</v>
       </c>
     </row>
     <row r="12" spans="1:48" ht="15">
-      <c r="B12" s="102"/>
-      <c r="R12" s="102" t="s">
+      <c r="B12" s="99"/>
+      <c r="R12" s="99" t="s">
         <v>1603</v>
       </c>
-      <c r="AG12" s="103" t="s">
+      <c r="AG12" s="100" t="s">
         <v>1604</v>
       </c>
-      <c r="AV12" s="103" t="s">
+      <c r="AV12" s="100" t="s">
         <v>1605</v>
       </c>
     </row>
     <row r="13" spans="1:48" ht="15">
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="99" t="s">
         <v>1606</v>
       </c>
-      <c r="R13" s="103" t="s">
+      <c r="R13" s="100" t="s">
         <v>1607</v>
       </c>
-      <c r="AG13" s="103" t="s">
+      <c r="AG13" s="100" t="s">
         <v>1608</v>
       </c>
-      <c r="AV13" s="103" t="s">
+      <c r="AV13" s="100" t="s">
         <v>1609</v>
       </c>
     </row>
     <row r="14" spans="1:48">
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="100" t="s">
         <v>1610</v>
       </c>
-      <c r="R14" s="103" t="s">
+      <c r="R14" s="100" t="s">
         <v>1611</v>
       </c>
-      <c r="AG14" s="103" t="s">
+      <c r="AG14" s="100" t="s">
         <v>1612</v>
       </c>
-      <c r="AV14" s="103" t="s">
+      <c r="AV14" s="100" t="s">
         <v>1613</v>
       </c>
     </row>
     <row r="15" spans="1:48">
-      <c r="B15" s="103" t="s">
+      <c r="B15" s="100" t="s">
         <v>1614</v>
       </c>
-      <c r="R15" s="103" t="s">
+      <c r="R15" s="100" t="s">
         <v>1615</v>
       </c>
-      <c r="AG15" s="103" t="s">
+      <c r="AG15" s="100" t="s">
         <v>1616</v>
       </c>
-      <c r="AV15" s="103" t="s">
+      <c r="AV15" s="100" t="s">
         <v>1617</v>
       </c>
     </row>
     <row r="16" spans="1:48">
-      <c r="B16" s="103" t="s">
+      <c r="B16" s="100" t="s">
         <v>1618</v>
       </c>
-      <c r="R16" s="103" t="s">
+      <c r="R16" s="100" t="s">
         <v>1619</v>
       </c>
-      <c r="AG16" s="102"/>
-      <c r="AV16" s="102"/>
+      <c r="AG16" s="99"/>
+      <c r="AV16" s="99"/>
     </row>
     <row r="17" spans="2:48" ht="15">
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="100" t="s">
         <v>1620</v>
       </c>
-      <c r="R17" s="102"/>
-      <c r="AG17" s="102" t="s">
+      <c r="R17" s="99"/>
+      <c r="AG17" s="99" t="s">
         <v>1621</v>
       </c>
-      <c r="AV17" s="102" t="s">
+      <c r="AV17" s="99" t="s">
         <v>1622</v>
       </c>
     </row>
     <row r="18" spans="2:48" ht="15">
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="100" t="s">
         <v>1623</v>
       </c>
-      <c r="R18" s="102" t="s">
+      <c r="R18" s="99" t="s">
         <v>1624</v>
       </c>
-      <c r="AG18" s="103" t="s">
+      <c r="AG18" s="100" t="s">
         <v>1625</v>
       </c>
-      <c r="AV18" s="103" t="s">
+      <c r="AV18" s="100" t="s">
         <v>1626</v>
       </c>
     </row>
     <row r="19" spans="2:48">
-      <c r="B19" s="102"/>
-      <c r="R19" s="103" t="s">
+      <c r="B19" s="99"/>
+      <c r="R19" s="100" t="s">
         <v>1627</v>
       </c>
-      <c r="AG19" s="103" t="s">
+      <c r="AG19" s="100" t="s">
         <v>1628</v>
       </c>
-      <c r="AV19" s="103" t="s">
+      <c r="AV19" s="100" t="s">
         <v>1629</v>
       </c>
     </row>
     <row r="20" spans="2:48" ht="15">
-      <c r="B20" s="102" t="s">
+      <c r="B20" s="99" t="s">
         <v>1630</v>
       </c>
-      <c r="R20" s="103" t="s">
+      <c r="R20" s="100" t="s">
         <v>1631</v>
       </c>
-      <c r="AG20" s="103" t="s">
+      <c r="AG20" s="100" t="s">
         <v>1632</v>
       </c>
-      <c r="AV20" s="103" t="s">
+      <c r="AV20" s="100" t="s">
         <v>1633</v>
       </c>
     </row>
     <row r="21" spans="2:48">
-      <c r="B21" s="103" t="s">
+      <c r="B21" s="100" t="s">
         <v>1634</v>
       </c>
-      <c r="R21" s="103" t="s">
+      <c r="R21" s="100" t="s">
         <v>1635</v>
       </c>
-      <c r="AG21" s="103" t="s">
+      <c r="AG21" s="100" t="s">
         <v>1636</v>
       </c>
     </row>
     <row r="22" spans="2:48">
-      <c r="B22" s="103" t="s">
+      <c r="B22" s="100" t="s">
         <v>1637</v>
       </c>
-      <c r="R22" s="103" t="s">
+      <c r="R22" s="100" t="s">
         <v>1638</v>
       </c>
-      <c r="AG22" s="102"/>
+      <c r="AG22" s="99"/>
     </row>
     <row r="23" spans="2:48" ht="15">
-      <c r="B23" s="103" t="s">
+      <c r="B23" s="100" t="s">
         <v>1639</v>
       </c>
-      <c r="AG23" s="102" t="s">
+      <c r="AG23" s="99" t="s">
         <v>1640</v>
       </c>
     </row>
     <row r="24" spans="2:48">
-      <c r="B24" s="103" t="s">
+      <c r="B24" s="100" t="s">
         <v>1641</v>
       </c>
-      <c r="AG24" s="103" t="s">
+      <c r="AG24" s="100" t="s">
         <v>1642</v>
       </c>
     </row>
     <row r="25" spans="2:48">
-      <c r="AG25" s="103" t="s">
+      <c r="AG25" s="100" t="s">
         <v>1643</v>
       </c>
     </row>
@@ -11617,29 +11617,29 @@
       <c r="BB13" s="15"/>
       <c r="BC13" s="16"/>
       <c r="BE13" s="13"/>
-      <c r="BF13" s="99" t="s">
+      <c r="BF13" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="BG13" s="99"/>
-      <c r="BH13" s="99"/>
-      <c r="BI13" s="99"/>
-      <c r="BJ13" s="99" t="s">
+      <c r="BG13" s="106"/>
+      <c r="BH13" s="106"/>
+      <c r="BI13" s="106"/>
+      <c r="BJ13" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="BK13" s="99"/>
-      <c r="BL13" s="99"/>
-      <c r="BM13" s="99"/>
-      <c r="BN13" s="99"/>
-      <c r="BO13" s="99"/>
-      <c r="BP13" s="99" t="s">
+      <c r="BK13" s="106"/>
+      <c r="BL13" s="106"/>
+      <c r="BM13" s="106"/>
+      <c r="BN13" s="106"/>
+      <c r="BO13" s="106"/>
+      <c r="BP13" s="106" t="s">
         <v>38</v>
       </c>
-      <c r="BQ13" s="99"/>
-      <c r="BR13" s="99"/>
-      <c r="BS13" s="99"/>
-      <c r="BT13" s="99"/>
-      <c r="BU13" s="99"/>
-      <c r="BV13" s="99"/>
+      <c r="BQ13" s="106"/>
+      <c r="BR13" s="106"/>
+      <c r="BS13" s="106"/>
+      <c r="BT13" s="106"/>
+      <c r="BU13" s="106"/>
+      <c r="BV13" s="106"/>
       <c r="BW13" s="16"/>
     </row>
     <row r="14" spans="2:75" ht="15.75" thickBot="1">
@@ -11664,29 +11664,29 @@
       <c r="BB14" s="22"/>
       <c r="BC14" s="23"/>
       <c r="BE14" s="13"/>
-      <c r="BF14" s="101" t="s">
+      <c r="BF14" s="108" t="s">
         <v>39</v>
       </c>
-      <c r="BG14" s="101"/>
-      <c r="BH14" s="101"/>
-      <c r="BI14" s="101"/>
-      <c r="BJ14" s="100" t="s">
+      <c r="BG14" s="108"/>
+      <c r="BH14" s="108"/>
+      <c r="BI14" s="108"/>
+      <c r="BJ14" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="BK14" s="100"/>
-      <c r="BL14" s="100"/>
-      <c r="BM14" s="100"/>
-      <c r="BN14" s="100"/>
-      <c r="BO14" s="100"/>
-      <c r="BP14" s="100" t="s">
+      <c r="BK14" s="107"/>
+      <c r="BL14" s="107"/>
+      <c r="BM14" s="107"/>
+      <c r="BN14" s="107"/>
+      <c r="BO14" s="107"/>
+      <c r="BP14" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="BQ14" s="100"/>
-      <c r="BR14" s="100"/>
-      <c r="BS14" s="100"/>
-      <c r="BT14" s="100"/>
-      <c r="BU14" s="100"/>
-      <c r="BV14" s="100"/>
+      <c r="BQ14" s="107"/>
+      <c r="BR14" s="107"/>
+      <c r="BS14" s="107"/>
+      <c r="BT14" s="107"/>
+      <c r="BU14" s="107"/>
+      <c r="BV14" s="107"/>
       <c r="BW14" s="16"/>
     </row>
     <row r="15" spans="2:75" ht="15.75" thickBot="1">
@@ -11695,29 +11695,29 @@
       </c>
       <c r="AL15" s="5"/>
       <c r="BE15" s="13"/>
-      <c r="BF15" s="101" t="s">
+      <c r="BF15" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="BG15" s="101"/>
-      <c r="BH15" s="101"/>
-      <c r="BI15" s="101"/>
-      <c r="BJ15" s="100" t="s">
+      <c r="BG15" s="108"/>
+      <c r="BH15" s="108"/>
+      <c r="BI15" s="108"/>
+      <c r="BJ15" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="BK15" s="100"/>
-      <c r="BL15" s="100"/>
-      <c r="BM15" s="100"/>
-      <c r="BN15" s="100"/>
-      <c r="BO15" s="100"/>
-      <c r="BP15" s="100" t="s">
+      <c r="BK15" s="107"/>
+      <c r="BL15" s="107"/>
+      <c r="BM15" s="107"/>
+      <c r="BN15" s="107"/>
+      <c r="BO15" s="107"/>
+      <c r="BP15" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="BQ15" s="100"/>
-      <c r="BR15" s="100"/>
-      <c r="BS15" s="100"/>
-      <c r="BT15" s="100"/>
-      <c r="BU15" s="100"/>
-      <c r="BV15" s="100"/>
+      <c r="BQ15" s="107"/>
+      <c r="BR15" s="107"/>
+      <c r="BS15" s="107"/>
+      <c r="BT15" s="107"/>
+      <c r="BU15" s="107"/>
+      <c r="BV15" s="107"/>
       <c r="BW15" s="16"/>
     </row>
     <row r="16" spans="2:75" ht="15">
@@ -11745,29 +11745,29 @@
       <c r="BB16" s="11"/>
       <c r="BC16" s="12"/>
       <c r="BE16" s="13"/>
-      <c r="BF16" s="101" t="s">
+      <c r="BF16" s="108" t="s">
         <v>44</v>
       </c>
-      <c r="BG16" s="101"/>
-      <c r="BH16" s="101"/>
-      <c r="BI16" s="101"/>
-      <c r="BJ16" s="100" t="s">
+      <c r="BG16" s="108"/>
+      <c r="BH16" s="108"/>
+      <c r="BI16" s="108"/>
+      <c r="BJ16" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="BK16" s="100"/>
-      <c r="BL16" s="100"/>
-      <c r="BM16" s="100"/>
-      <c r="BN16" s="100"/>
-      <c r="BO16" s="100"/>
-      <c r="BP16" s="100" t="s">
+      <c r="BK16" s="107"/>
+      <c r="BL16" s="107"/>
+      <c r="BM16" s="107"/>
+      <c r="BN16" s="107"/>
+      <c r="BO16" s="107"/>
+      <c r="BP16" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="BQ16" s="100"/>
-      <c r="BR16" s="100"/>
-      <c r="BS16" s="100"/>
-      <c r="BT16" s="100"/>
-      <c r="BU16" s="100"/>
-      <c r="BV16" s="100"/>
+      <c r="BQ16" s="107"/>
+      <c r="BR16" s="107"/>
+      <c r="BS16" s="107"/>
+      <c r="BT16" s="107"/>
+      <c r="BU16" s="107"/>
+      <c r="BV16" s="107"/>
       <c r="BW16" s="16"/>
     </row>
     <row r="17" spans="2:88" ht="15">
@@ -12278,33 +12278,33 @@
         <v>192</v>
       </c>
       <c r="AL28" s="13"/>
-      <c r="AM28" s="99" t="s">
+      <c r="AM28" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="AN28" s="99"/>
-      <c r="AO28" s="99"/>
-      <c r="AP28" s="99" t="s">
+      <c r="AN28" s="106"/>
+      <c r="AO28" s="106"/>
+      <c r="AP28" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="AQ28" s="99"/>
-      <c r="AR28" s="99"/>
-      <c r="AS28" s="99"/>
-      <c r="AT28" s="99"/>
-      <c r="AU28" s="99"/>
-      <c r="AV28" s="99"/>
-      <c r="AW28" s="99"/>
-      <c r="AX28" s="99" t="s">
+      <c r="AQ28" s="106"/>
+      <c r="AR28" s="106"/>
+      <c r="AS28" s="106"/>
+      <c r="AT28" s="106"/>
+      <c r="AU28" s="106"/>
+      <c r="AV28" s="106"/>
+      <c r="AW28" s="106"/>
+      <c r="AX28" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="AY28" s="99"/>
-      <c r="AZ28" s="99"/>
-      <c r="BA28" s="99"/>
-      <c r="BB28" s="99" t="s">
+      <c r="AY28" s="106"/>
+      <c r="AZ28" s="106"/>
+      <c r="BA28" s="106"/>
+      <c r="BB28" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="BC28" s="99"/>
-      <c r="BD28" s="99"/>
-      <c r="BE28" s="99"/>
+      <c r="BC28" s="106"/>
+      <c r="BD28" s="106"/>
+      <c r="BE28" s="106"/>
       <c r="BF28" s="16"/>
       <c r="BH28" s="21" t="s">
         <v>71</v>
@@ -12340,33 +12340,33 @@
     </row>
     <row r="29" spans="2:88" ht="15" thickBot="1">
       <c r="AL29" s="13"/>
-      <c r="AM29" s="101" t="s">
+      <c r="AM29" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="AN29" s="101"/>
-      <c r="AO29" s="101"/>
-      <c r="AP29" s="100" t="s">
+      <c r="AN29" s="108"/>
+      <c r="AO29" s="108"/>
+      <c r="AP29" s="107" t="s">
         <v>193</v>
       </c>
-      <c r="AQ29" s="100"/>
-      <c r="AR29" s="100"/>
-      <c r="AS29" s="100"/>
-      <c r="AT29" s="100"/>
-      <c r="AU29" s="100"/>
-      <c r="AV29" s="100"/>
-      <c r="AW29" s="100"/>
-      <c r="AX29" s="100" t="s">
+      <c r="AQ29" s="107"/>
+      <c r="AR29" s="107"/>
+      <c r="AS29" s="107"/>
+      <c r="AT29" s="107"/>
+      <c r="AU29" s="107"/>
+      <c r="AV29" s="107"/>
+      <c r="AW29" s="107"/>
+      <c r="AX29" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="AY29" s="100"/>
-      <c r="AZ29" s="100"/>
-      <c r="BA29" s="100"/>
-      <c r="BB29" s="101" t="s">
+      <c r="AY29" s="107"/>
+      <c r="AZ29" s="107"/>
+      <c r="BA29" s="107"/>
+      <c r="BB29" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="BC29" s="101"/>
-      <c r="BD29" s="101"/>
-      <c r="BE29" s="101"/>
+      <c r="BC29" s="108"/>
+      <c r="BD29" s="108"/>
+      <c r="BE29" s="108"/>
       <c r="BF29" s="16"/>
     </row>
     <row r="30" spans="2:88" ht="15">
@@ -12374,33 +12374,33 @@
         <v>4</v>
       </c>
       <c r="AL30" s="13"/>
-      <c r="AM30" s="101" t="s">
+      <c r="AM30" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="AN30" s="101"/>
-      <c r="AO30" s="101"/>
-      <c r="AP30" s="100" t="s">
+      <c r="AN30" s="108"/>
+      <c r="AO30" s="108"/>
+      <c r="AP30" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="AQ30" s="100"/>
-      <c r="AR30" s="100"/>
-      <c r="AS30" s="100"/>
-      <c r="AT30" s="100"/>
-      <c r="AU30" s="100"/>
-      <c r="AV30" s="100"/>
-      <c r="AW30" s="100"/>
-      <c r="AX30" s="100" t="s">
+      <c r="AQ30" s="107"/>
+      <c r="AR30" s="107"/>
+      <c r="AS30" s="107"/>
+      <c r="AT30" s="107"/>
+      <c r="AU30" s="107"/>
+      <c r="AV30" s="107"/>
+      <c r="AW30" s="107"/>
+      <c r="AX30" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="AY30" s="100"/>
-      <c r="AZ30" s="100"/>
-      <c r="BA30" s="100"/>
-      <c r="BB30" s="101" t="s">
+      <c r="AY30" s="107"/>
+      <c r="AZ30" s="107"/>
+      <c r="BA30" s="107"/>
+      <c r="BB30" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="BC30" s="101"/>
-      <c r="BD30" s="101"/>
-      <c r="BE30" s="101"/>
+      <c r="BC30" s="108"/>
+      <c r="BD30" s="108"/>
+      <c r="BE30" s="108"/>
       <c r="BF30" s="16"/>
       <c r="BH30" s="10" t="s">
         <v>72</v>
@@ -12432,33 +12432,33 @@
         <v>5</v>
       </c>
       <c r="AL31" s="13"/>
-      <c r="AM31" s="101" t="s">
+      <c r="AM31" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="AN31" s="101"/>
-      <c r="AO31" s="101"/>
-      <c r="AP31" s="100" t="s">
+      <c r="AN31" s="108"/>
+      <c r="AO31" s="108"/>
+      <c r="AP31" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="AQ31" s="100"/>
-      <c r="AR31" s="100"/>
-      <c r="AS31" s="100"/>
-      <c r="AT31" s="100"/>
-      <c r="AU31" s="100"/>
-      <c r="AV31" s="100"/>
-      <c r="AW31" s="100"/>
-      <c r="AX31" s="100" t="s">
+      <c r="AQ31" s="107"/>
+      <c r="AR31" s="107"/>
+      <c r="AS31" s="107"/>
+      <c r="AT31" s="107"/>
+      <c r="AU31" s="107"/>
+      <c r="AV31" s="107"/>
+      <c r="AW31" s="107"/>
+      <c r="AX31" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="AY31" s="100"/>
-      <c r="AZ31" s="100"/>
-      <c r="BA31" s="100"/>
-      <c r="BB31" s="101" t="s">
+      <c r="AY31" s="107"/>
+      <c r="AZ31" s="107"/>
+      <c r="BA31" s="107"/>
+      <c r="BB31" s="108" t="s">
         <v>63</v>
       </c>
-      <c r="BC31" s="101"/>
-      <c r="BD31" s="101"/>
-      <c r="BE31" s="101"/>
+      <c r="BC31" s="108"/>
+      <c r="BD31" s="108"/>
+      <c r="BE31" s="108"/>
       <c r="BF31" s="16"/>
       <c r="BH31" s="19" t="s">
         <v>73</v>
@@ -17782,6 +17782,22 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="AX28:BA28"/>
+    <mergeCell ref="AX29:BA29"/>
+    <mergeCell ref="AX30:BA30"/>
+    <mergeCell ref="AX31:BA31"/>
+    <mergeCell ref="BB28:BE28"/>
+    <mergeCell ref="BB29:BE29"/>
+    <mergeCell ref="BB30:BE30"/>
+    <mergeCell ref="BB31:BE31"/>
+    <mergeCell ref="AM28:AO28"/>
+    <mergeCell ref="AM29:AO29"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="AM31:AO31"/>
+    <mergeCell ref="AP28:AW28"/>
+    <mergeCell ref="AP29:AW29"/>
+    <mergeCell ref="AP30:AW30"/>
+    <mergeCell ref="AP31:AW31"/>
     <mergeCell ref="BP13:BV13"/>
     <mergeCell ref="BP14:BV14"/>
     <mergeCell ref="BP15:BV15"/>
@@ -17794,22 +17810,6 @@
     <mergeCell ref="BJ14:BO14"/>
     <mergeCell ref="BJ15:BO15"/>
     <mergeCell ref="BJ16:BO16"/>
-    <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AM31:AO31"/>
-    <mergeCell ref="AP28:AW28"/>
-    <mergeCell ref="AP29:AW29"/>
-    <mergeCell ref="AP30:AW30"/>
-    <mergeCell ref="AP31:AW31"/>
-    <mergeCell ref="AX28:BA28"/>
-    <mergeCell ref="AX29:BA29"/>
-    <mergeCell ref="AX30:BA30"/>
-    <mergeCell ref="AX31:BA31"/>
-    <mergeCell ref="BB28:BE28"/>
-    <mergeCell ref="BB29:BE29"/>
-    <mergeCell ref="BB30:BE30"/>
-    <mergeCell ref="BB31:BE31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -22596,111 +22596,293 @@
         <v>313</v>
       </c>
     </row>
-    <row r="191" spans="1:39">
+    <row r="191" spans="1:39" ht="15">
       <c r="B191" s="7" t="s">
         <v>1024</v>
       </c>
-      <c r="V191" s="7" t="s">
+      <c r="V191" s="94" t="s">
         <v>1042</v>
       </c>
-    </row>
-    <row r="192" spans="1:39">
+      <c r="W191" s="59"/>
+      <c r="X191" s="59"/>
+      <c r="Y191" s="59"/>
+      <c r="Z191" s="59"/>
+      <c r="AA191" s="59"/>
+      <c r="AB191" s="59"/>
+      <c r="AC191" s="59"/>
+      <c r="AD191" s="59"/>
+      <c r="AE191" s="59"/>
+      <c r="AF191" s="59"/>
+      <c r="AG191" s="59"/>
+      <c r="AH191" s="59"/>
+      <c r="AI191" s="59"/>
+      <c r="AJ191" s="59"/>
+    </row>
+    <row r="192" spans="1:39" ht="15">
       <c r="B192" s="7" t="s">
         <v>1025</v>
       </c>
-      <c r="V192" s="7" t="s">
+      <c r="V192" s="94" t="s">
         <v>1043</v>
       </c>
-    </row>
-    <row r="193" spans="2:22">
+      <c r="W192" s="59"/>
+      <c r="X192" s="59"/>
+      <c r="Y192" s="59"/>
+      <c r="Z192" s="59"/>
+      <c r="AA192" s="59"/>
+      <c r="AB192" s="59"/>
+      <c r="AC192" s="59"/>
+      <c r="AD192" s="59"/>
+      <c r="AE192" s="59"/>
+      <c r="AF192" s="59"/>
+      <c r="AG192" s="59"/>
+      <c r="AH192" s="59"/>
+      <c r="AI192" s="59"/>
+      <c r="AJ192" s="59"/>
+    </row>
+    <row r="193" spans="2:36" ht="15">
       <c r="B193" s="7" t="s">
         <v>1026</v>
       </c>
-      <c r="V193" s="7" t="s">
+      <c r="V193" s="94" t="s">
         <v>1044</v>
       </c>
-    </row>
-    <row r="194" spans="2:22">
+      <c r="W193" s="59"/>
+      <c r="X193" s="59"/>
+      <c r="Y193" s="59"/>
+      <c r="Z193" s="59"/>
+      <c r="AA193" s="59"/>
+      <c r="AB193" s="59"/>
+      <c r="AC193" s="59"/>
+      <c r="AD193" s="59"/>
+      <c r="AE193" s="59"/>
+      <c r="AF193" s="59"/>
+      <c r="AG193" s="59"/>
+      <c r="AH193" s="59"/>
+      <c r="AI193" s="59"/>
+      <c r="AJ193" s="59"/>
+    </row>
+    <row r="194" spans="2:36" ht="15">
       <c r="B194" s="7" t="s">
         <v>1027</v>
       </c>
-      <c r="V194" s="7" t="s">
+      <c r="V194" s="94" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="195" spans="2:22">
+      <c r="W194" s="59"/>
+      <c r="X194" s="59"/>
+      <c r="Y194" s="59"/>
+      <c r="Z194" s="59"/>
+      <c r="AA194" s="59"/>
+      <c r="AB194" s="59"/>
+      <c r="AC194" s="59"/>
+      <c r="AD194" s="59"/>
+      <c r="AE194" s="59"/>
+      <c r="AF194" s="59"/>
+      <c r="AG194" s="59"/>
+      <c r="AH194" s="59"/>
+      <c r="AI194" s="59"/>
+      <c r="AJ194" s="59"/>
+    </row>
+    <row r="195" spans="2:36" ht="15">
       <c r="B195" s="7" t="s">
         <v>1028</v>
       </c>
-      <c r="V195" s="7" t="s">
+      <c r="V195" s="94" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="196" spans="2:22">
+      <c r="W195" s="59"/>
+      <c r="X195" s="59"/>
+      <c r="Y195" s="59"/>
+      <c r="Z195" s="59"/>
+      <c r="AA195" s="59"/>
+      <c r="AB195" s="59"/>
+      <c r="AC195" s="59"/>
+      <c r="AD195" s="59"/>
+      <c r="AE195" s="59"/>
+      <c r="AF195" s="59"/>
+      <c r="AG195" s="59"/>
+      <c r="AH195" s="59"/>
+      <c r="AI195" s="59"/>
+      <c r="AJ195" s="59"/>
+    </row>
+    <row r="196" spans="2:36" ht="15">
       <c r="B196" s="7" t="s">
         <v>1029</v>
       </c>
-      <c r="V196" s="7" t="s">
+      <c r="V196" s="94" t="s">
         <v>1046</v>
       </c>
-    </row>
-    <row r="197" spans="2:22">
+      <c r="W196" s="59"/>
+      <c r="X196" s="59"/>
+      <c r="Y196" s="59"/>
+      <c r="Z196" s="59"/>
+      <c r="AA196" s="59"/>
+      <c r="AB196" s="59"/>
+      <c r="AC196" s="59"/>
+      <c r="AD196" s="59"/>
+      <c r="AE196" s="59"/>
+      <c r="AF196" s="59"/>
+      <c r="AG196" s="59"/>
+      <c r="AH196" s="59"/>
+      <c r="AI196" s="59"/>
+      <c r="AJ196" s="59"/>
+    </row>
+    <row r="197" spans="2:36" ht="15">
       <c r="B197" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="V197" s="7" t="s">
+      <c r="V197" s="94" t="s">
         <v>1047</v>
       </c>
-    </row>
-    <row r="198" spans="2:22">
+      <c r="W197" s="59"/>
+      <c r="X197" s="59"/>
+      <c r="Y197" s="59"/>
+      <c r="Z197" s="59"/>
+      <c r="AA197" s="59"/>
+      <c r="AB197" s="59"/>
+      <c r="AC197" s="59"/>
+      <c r="AD197" s="59"/>
+      <c r="AE197" s="59"/>
+      <c r="AF197" s="59"/>
+      <c r="AG197" s="59"/>
+      <c r="AH197" s="59"/>
+      <c r="AI197" s="59"/>
+      <c r="AJ197" s="59"/>
+    </row>
+    <row r="198" spans="2:36" ht="15">
       <c r="B198" s="7" t="s">
         <v>1030</v>
       </c>
-      <c r="V198" s="7" t="s">
+      <c r="V198" s="94" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="199" spans="2:22">
+      <c r="W198" s="59"/>
+      <c r="X198" s="59"/>
+      <c r="Y198" s="59"/>
+      <c r="Z198" s="59"/>
+      <c r="AA198" s="59"/>
+      <c r="AB198" s="59"/>
+      <c r="AC198" s="59"/>
+      <c r="AD198" s="59"/>
+      <c r="AE198" s="59"/>
+      <c r="AF198" s="59"/>
+      <c r="AG198" s="59"/>
+      <c r="AH198" s="59"/>
+      <c r="AI198" s="59"/>
+      <c r="AJ198" s="59"/>
+    </row>
+    <row r="199" spans="2:36" ht="15">
       <c r="B199" s="7" t="s">
         <v>1031</v>
       </c>
-      <c r="V199" s="7" t="s">
+      <c r="V199" s="94" t="s">
         <v>1048</v>
       </c>
-    </row>
-    <row r="200" spans="2:22">
+      <c r="W199" s="59"/>
+      <c r="X199" s="59"/>
+      <c r="Y199" s="59"/>
+      <c r="Z199" s="59"/>
+      <c r="AA199" s="59"/>
+      <c r="AB199" s="59"/>
+      <c r="AC199" s="59"/>
+      <c r="AD199" s="59"/>
+      <c r="AE199" s="59"/>
+      <c r="AF199" s="59"/>
+      <c r="AG199" s="59"/>
+      <c r="AH199" s="59"/>
+      <c r="AI199" s="59"/>
+      <c r="AJ199" s="59"/>
+    </row>
+    <row r="200" spans="2:36" ht="15">
       <c r="B200" s="7" t="s">
         <v>1032</v>
       </c>
-      <c r="V200" s="7" t="s">
+      <c r="V200" s="94" t="s">
         <v>1049</v>
       </c>
-    </row>
-    <row r="201" spans="2:22">
+      <c r="W200" s="59"/>
+      <c r="X200" s="59"/>
+      <c r="Y200" s="59"/>
+      <c r="Z200" s="59"/>
+      <c r="AA200" s="59"/>
+      <c r="AB200" s="59"/>
+      <c r="AC200" s="59"/>
+      <c r="AD200" s="59"/>
+      <c r="AE200" s="59"/>
+      <c r="AF200" s="59"/>
+      <c r="AG200" s="59"/>
+      <c r="AH200" s="59"/>
+      <c r="AI200" s="59"/>
+      <c r="AJ200" s="59"/>
+    </row>
+    <row r="201" spans="2:36" ht="15">
       <c r="B201" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="V201" s="7" t="s">
+      <c r="V201" s="94" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="202" spans="2:22">
+      <c r="W201" s="59"/>
+      <c r="X201" s="59"/>
+      <c r="Y201" s="59"/>
+      <c r="Z201" s="59"/>
+      <c r="AA201" s="59"/>
+      <c r="AB201" s="59"/>
+      <c r="AC201" s="59"/>
+      <c r="AD201" s="59"/>
+      <c r="AE201" s="59"/>
+      <c r="AF201" s="59"/>
+      <c r="AG201" s="59"/>
+      <c r="AH201" s="59"/>
+      <c r="AI201" s="59"/>
+      <c r="AJ201" s="59"/>
+    </row>
+    <row r="202" spans="2:36" ht="15">
       <c r="B202" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="V202" s="7" t="s">
+      <c r="V202" s="94" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="203" spans="2:22">
+      <c r="W202" s="59"/>
+      <c r="X202" s="59"/>
+      <c r="Y202" s="59"/>
+      <c r="Z202" s="59"/>
+      <c r="AA202" s="59"/>
+      <c r="AB202" s="59"/>
+      <c r="AC202" s="59"/>
+      <c r="AD202" s="59"/>
+      <c r="AE202" s="59"/>
+      <c r="AF202" s="59"/>
+      <c r="AG202" s="59"/>
+      <c r="AH202" s="59"/>
+      <c r="AI202" s="59"/>
+      <c r="AJ202" s="59"/>
+    </row>
+    <row r="203" spans="2:36" ht="15">
       <c r="B203" s="7" t="s">
         <v>1033</v>
       </c>
-      <c r="V203" s="7" t="s">
+      <c r="V203" s="94" t="s">
         <v>1052</v>
       </c>
-    </row>
-    <row r="204" spans="2:22">
+      <c r="W203" s="59"/>
+      <c r="X203" s="59"/>
+      <c r="Y203" s="59"/>
+      <c r="Z203" s="59"/>
+      <c r="AA203" s="59"/>
+      <c r="AB203" s="59"/>
+      <c r="AC203" s="59"/>
+      <c r="AD203" s="59"/>
+      <c r="AE203" s="59"/>
+      <c r="AF203" s="59"/>
+      <c r="AG203" s="59"/>
+      <c r="AH203" s="59"/>
+      <c r="AI203" s="59"/>
+      <c r="AJ203" s="59"/>
+    </row>
+    <row r="204" spans="2:36">
       <c r="B204" s="7" t="s">
         <v>1034</v>
       </c>
@@ -22708,7 +22890,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="205" spans="2:22">
+    <row r="205" spans="2:36">
       <c r="B205" s="7" t="s">
         <v>1035</v>
       </c>
@@ -22716,7 +22898,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="206" spans="2:22">
+    <row r="206" spans="2:36">
       <c r="B206" s="7" t="s">
         <v>313</v>
       </c>
@@ -22724,7 +22906,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="207" spans="2:22">
+    <row r="207" spans="2:36">
       <c r="B207" s="7" t="s">
         <v>1036</v>
       </c>
@@ -22732,7 +22914,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="208" spans="2:22">
+    <row r="208" spans="2:36">
       <c r="B208" s="7" t="s">
         <v>1037</v>
       </c>
